--- a/data/administracion_de_tribunales/OP_LEY148Archivadas.xlsx
+++ b/data/administracion_de_tribunales/OP_LEY148Archivadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6164E3-32BF-4FF2-B0AE-B68DF00C0922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE5630A-5D55-4BF9-BAEF-7F2CACC54D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="21">
   <si>
     <t>Región</t>
   </si>
@@ -783,7 +783,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
@@ -940,44 +940,30 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="3">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15">
         <f>SUM(B2:B14)</f>
         <v>8</v>
       </c>
-      <c r="C16">
-        <f t="shared" ref="C16:D16" si="0">SUM(C2:C14)</f>
+      <c r="C15">
+        <f>SUM(C2:C14)</f>
         <v>3</v>
       </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
+      <c r="D15">
+        <f>SUM(D2:D14)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1158,6 +1144,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37247A8D-E653-4823-BD28-94768F3C7E21}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1182,6 +1172,12 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1192,11 +1188,26 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1207,11 +1218,23 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1227,6 +1250,12 @@
       <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -1255,15 +1284,15 @@
       </c>
       <c r="B16">
         <f>SUM(B2:B15)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C16">
         <f t="shared" ref="C16:D16" si="0">SUM(C2:C15)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
